--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,9 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,8 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,16 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -516,8 +516,9 @@
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -517,8 +517,9 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -518,8 +518,9 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -519,8 +519,9 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -520,8 +520,9 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -521,8 +521,9 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -522,8 +522,9 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -523,8 +523,9 @@
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -524,8 +524,9 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -525,8 +525,9 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -526,8 +526,9 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -527,8 +527,9 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -528,8 +528,9 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -529,8 +529,9 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,8 +530,9 @@
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -531,8 +531,9 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -532,8 +532,9 @@
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -533,8 +533,9 @@
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -534,8 +534,9 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -535,8 +535,9 @@
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -536,8 +536,9 @@
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -537,8 +537,9 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -538,8 +538,9 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -539,8 +539,9 @@
     <row r="31"/>
     <row r="32"/>
     <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -540,8 +540,9 @@
     <row r="32"/>
     <row r="33"/>
     <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -541,8 +541,9 @@
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -542,8 +542,9 @@
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -543,8 +543,9 @@
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -544,8 +544,9 @@
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -545,8 +545,9 @@
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -546,8 +546,9 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -547,8 +547,9 @@
     <row r="39"/>
     <row r="40"/>
     <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -548,8 +548,9 @@
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -549,8 +549,9 @@
     <row r="41"/>
     <row r="42"/>
     <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -550,8 +550,9 @@
     <row r="42"/>
     <row r="43"/>
     <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -551,8 +551,9 @@
     <row r="43"/>
     <row r="44"/>
     <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,8 +552,9 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -553,8 +553,9 @@
     <row r="45"/>
     <row r="46"/>
     <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -554,8 +554,9 @@
     <row r="46"/>
     <row r="47"/>
     <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -555,8 +555,9 @@
     <row r="47"/>
     <row r="48"/>
     <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -556,8 +556,9 @@
     <row r="48"/>
     <row r="49"/>
     <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -557,8 +557,9 @@
     <row r="49"/>
     <row r="50"/>
     <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -558,8 +558,9 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,8 +559,9 @@
     <row r="51"/>
     <row r="52"/>
     <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -560,8 +560,9 @@
     <row r="52"/>
     <row r="53"/>
     <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -561,8 +561,9 @@
     <row r="53"/>
     <row r="54"/>
     <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -562,8 +562,9 @@
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -563,8 +563,9 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -564,8 +564,9 @@
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -565,8 +565,9 @@
     <row r="57"/>
     <row r="58"/>
     <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -566,8 +566,9 @@
     <row r="58"/>
     <row r="59"/>
     <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -567,8 +567,9 @@
     <row r="59"/>
     <row r="60"/>
     <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -568,8 +568,9 @@
     <row r="60"/>
     <row r="61"/>
     <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -569,8 +569,9 @@
     <row r="61"/>
     <row r="62"/>
     <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -570,8 +570,9 @@
     <row r="62"/>
     <row r="63"/>
     <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -571,8 +571,9 @@
     <row r="63"/>
     <row r="64"/>
     <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -572,8 +572,9 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -573,8 +573,9 @@
     <row r="65"/>
     <row r="66"/>
     <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -574,8 +574,9 @@
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -575,8 +575,9 @@
     <row r="67"/>
     <row r="68"/>
     <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -576,8 +576,9 @@
     <row r="68"/>
     <row r="69"/>
     <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -577,8 +577,9 @@
     <row r="69"/>
     <row r="70"/>
     <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -578,8 +578,9 @@
     <row r="70"/>
     <row r="71"/>
     <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -579,8 +579,9 @@
     <row r="71"/>
     <row r="72"/>
     <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -580,8 +580,9 @@
     <row r="72"/>
     <row r="73"/>
     <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -581,8 +581,9 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -582,8 +582,9 @@
     <row r="74"/>
     <row r="75"/>
     <row r="76"/>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -583,8 +583,9 @@
     <row r="75"/>
     <row r="76"/>
     <row r="77"/>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -584,8 +584,9 @@
     <row r="76"/>
     <row r="77"/>
     <row r="78"/>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -585,8 +585,9 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -586,8 +586,9 @@
     <row r="78"/>
     <row r="79"/>
     <row r="80"/>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -587,8 +587,9 @@
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -588,8 +588,9 @@
     <row r="80"/>
     <row r="81"/>
     <row r="82"/>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -589,8 +589,9 @@
     <row r="81"/>
     <row r="82"/>
     <row r="83"/>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -590,8 +590,9 @@
     <row r="82"/>
     <row r="83"/>
     <row r="84"/>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -591,8 +591,9 @@
     <row r="83"/>
     <row r="84"/>
     <row r="85"/>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -592,8 +592,9 @@
     <row r="84"/>
     <row r="85"/>
     <row r="86"/>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -593,8 +593,9 @@
     <row r="85"/>
     <row r="86"/>
     <row r="87"/>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -594,8 +594,9 @@
     <row r="86"/>
     <row r="87"/>
     <row r="88"/>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -595,8 +595,9 @@
     <row r="87"/>
     <row r="88"/>
     <row r="89"/>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -596,8 +596,9 @@
     <row r="88"/>
     <row r="89"/>
     <row r="90"/>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -597,8 +597,9 @@
     <row r="89"/>
     <row r="90"/>
     <row r="91"/>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -598,8 +598,9 @@
     <row r="90"/>
     <row r="91"/>
     <row r="92"/>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -599,8 +599,9 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93"/>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -600,8 +600,9 @@
     <row r="92"/>
     <row r="93"/>
     <row r="94"/>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -601,8 +601,9 @@
     <row r="93"/>
     <row r="94"/>
     <row r="95"/>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -602,8 +602,9 @@
     <row r="94"/>
     <row r="95"/>
     <row r="96"/>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -603,8 +603,9 @@
     <row r="95"/>
     <row r="96"/>
     <row r="97"/>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -604,8 +604,9 @@
     <row r="96"/>
     <row r="97"/>
     <row r="98"/>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -605,8 +605,9 @@
     <row r="97"/>
     <row r="98"/>
     <row r="99"/>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -606,8 +606,9 @@
     <row r="98"/>
     <row r="99"/>
     <row r="100"/>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -607,8 +607,9 @@
     <row r="99"/>
     <row r="100"/>
     <row r="101"/>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -608,8 +608,9 @@
     <row r="100"/>
     <row r="101"/>
     <row r="102"/>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -609,8 +609,9 @@
     <row r="101"/>
     <row r="102"/>
     <row r="103"/>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -610,8 +610,9 @@
     <row r="102"/>
     <row r="103"/>
     <row r="104"/>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -611,8 +611,9 @@
     <row r="103"/>
     <row r="104"/>
     <row r="105"/>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
+    <row r="106"/>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -612,8 +612,9 @@
     <row r="104"/>
     <row r="105"/>
     <row r="106"/>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -613,8 +613,9 @@
     <row r="105"/>
     <row r="106"/>
     <row r="107"/>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
